--- a/results/regression_output/robustness/sample_restrictions.xlsx
+++ b/results/regression_output/robustness/sample_restrictions.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1154315327473594</v>
+        <v>-0.1012746800182213</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05483296800165782</v>
+        <v>0.05275385897832809</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03618212557027589</v>
+        <v>0.05591911331221877</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6091572353765752</v>
+        <v>-0.5950760110920711</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06195681360182555</v>
+        <v>0.06080434296142238</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -499,7 +499,7 @@
         <v>33</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4077433673083015</v>
+        <v>0.403069015694194</v>
       </c>
     </row>
     <row r="3">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1154315327473594</v>
+        <v>-0.1012746800182213</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05483296800165782</v>
+        <v>0.05275385897832809</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03618212557027589</v>
+        <v>0.05591911331221877</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6091572353765752</v>
+        <v>-0.5950760110920711</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06195681360182555</v>
+        <v>0.06080434296142238</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>33</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4077433673083015</v>
+        <v>0.403069015694194</v>
       </c>
     </row>
     <row r="4">
@@ -543,31 +543,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1214765169860027</v>
+        <v>-0.1039838481710088</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05752870230605787</v>
+        <v>0.05703918132115823</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03568785208925851</v>
+        <v>0.06946588642474416</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6083807014104927</v>
+        <v>-0.5938082427601081</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06315417999430789</v>
+        <v>0.06234329435715342</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I4" t="n">
         <v>31</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4050799868227309</v>
+        <v>0.4006228644070322</v>
       </c>
     </row>
     <row r="5">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.09037436491856517</v>
+        <v>-0.01561720574810096</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02702066667814423</v>
+        <v>0.03690358428543064</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001070808726658656</v>
+        <v>0.6728405877183565</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -595,7 +595,7 @@
         <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3705731049085903</v>
+        <v>0.3553462372113894</v>
       </c>
     </row>
     <row r="6">
@@ -605,22 +605,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.005982570377965526</v>
+        <v>-0.008124934146793378</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1339499060293884</v>
+        <v>0.1195635959687308</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9644485578524769</v>
+        <v>0.9459318663748957</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4292510684241173</v>
+        <v>-0.4325845987107261</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09517570614928891</v>
+        <v>0.08916486102726136</v>
       </c>
       <c r="G6" t="n">
-        <v>1.491239467643624e-05</v>
+        <v>3.630659124453928e-06</v>
       </c>
       <c r="H6" t="n">
         <v>160</v>
@@ -629,7 +629,7 @@
         <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5164704723696156</v>
+        <v>0.522826261129786</v>
       </c>
     </row>
   </sheetData>
